--- a/Ready_models/hf_aft_final_summary.xlsx
+++ b/Ready_models/hf_aft_final_summary.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>mu_</t>
+          <t>lambda_</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -528,37 +528,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.04496731560723439</v>
+        <v>-0.04684411452857535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9560287285409161</v>
+        <v>0.9542361375470227</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0104227713720508</v>
+        <v>0.009567411737428994</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.06539557211554908</v>
+        <v>-0.06559589695920195</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02453905909891969</v>
+        <v>-0.02809233209794874</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9366968589237296</v>
+        <v>0.9365092340655031</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9757595758842854</v>
+        <v>0.9722985882881023</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.314333875519573</v>
+        <v>-4.896216010576289</v>
       </c>
       <c r="L2" t="n">
-        <v>1.600848581820624e-05</v>
+        <v>9.769966943589897e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>15.93080361916687</v>
+        <v>19.96514298332797</v>
       </c>
     </row>
     <row r="3">
@@ -569,201 +569,201 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.4160250566813602</v>
+        <v>-0.4350991129028531</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6596637412931361</v>
+        <v>0.6472005179770206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2468342848442047</v>
+        <v>0.2203087901732207</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8998113651257025</v>
+        <v>-0.8668964071199574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06776125176298203</v>
+        <v>-0.003301818685748803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.40664636019122</v>
+        <v>0.4202538241131432</v>
       </c>
       <c r="I3" t="n">
-        <v>1.070109791151779</v>
+        <v>0.9967036263231087</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.685442753400097</v>
+        <v>-1.974951215340753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09190318089673682</v>
+        <v>0.04827368449668124</v>
       </c>
       <c r="M3" t="n">
-        <v>3.443741393717108</v>
+        <v>4.372619244860289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ejection_fraction</t>
+          <t>creatinine_phosphokinase</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04349734750539298</v>
+        <v>-0.0002182910785044066</v>
       </c>
       <c r="D4" t="n">
-        <v>1.044457223891198</v>
+        <v>0.9997817327452595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01130969415850349</v>
+        <v>0.0001032045617680758</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0213307542785631</v>
+        <v>-0.0004205683026100744</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06566394073222287</v>
+        <v>-1.601385439873869e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.021559881066656</v>
+        <v>0.9995795201238415</v>
       </c>
       <c r="I4" t="n">
-        <v>1.067867789991382</v>
+        <v>0.9999839862738222</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3.846023322627902</v>
+        <v>-2.115130133442711</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001200503408569799</v>
+        <v>0.03441885759061868</v>
       </c>
       <c r="M4" t="n">
-        <v>13.02407287975474</v>
+        <v>4.860656976641261</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>high_blood_pressure</t>
+          <t>ejection_fraction</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.4813305965238072</v>
+        <v>0.05560107306304598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6179605883071486</v>
+        <v>1.057175863675395</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2533726256327745</v>
+        <v>0.01119382372671492</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9779318174323952</v>
+        <v>0.0336615817093948</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01527062438478083</v>
+        <v>0.07754056441669716</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3760881139510489</v>
+        <v>1.034234543611244</v>
       </c>
       <c r="I5" t="n">
-        <v>1.015387816139868</v>
+        <v>1.080626066535559</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.89969455193405</v>
+        <v>4.967120656934211</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05747321571259879</v>
+        <v>6.795431123907898e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>4.120966417392266</v>
+        <v>20.48893158112272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>serum_creatinine</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.362078984034458</v>
+        <v>-0.5038505129039412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6962273748230506</v>
+        <v>0.6041996961633785</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1048644316995259</v>
+        <v>0.2199640865654362</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5676094934247893</v>
+        <v>-0.934972200464447</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1565484746441269</v>
+        <v>-0.0727288253434355</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5668789481212285</v>
+        <v>0.3925967793879442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8550900665115816</v>
+        <v>0.929852948394128</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.452829316540271</v>
+        <v>-2.290603528835844</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005547398900446077</v>
+        <v>0.0219863546597042</v>
       </c>
       <c r="M6" t="n">
-        <v>10.81590090953891</v>
+        <v>5.507247764768925</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>serum_sodium</t>
+          <t>serum_creatinine</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.05668600969788514</v>
+        <v>-0.3619073142508487</v>
       </c>
       <c r="D7" t="n">
-        <v>1.058323454918687</v>
+        <v>0.6963469062855061</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02682142076365551</v>
+        <v>0.06869758333583387</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004116990986925549</v>
+        <v>-0.496552103414022</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1092550284088447</v>
+        <v>-0.2272625250876753</v>
       </c>
       <c r="H7" t="n">
-        <v>1.004125477436534</v>
+        <v>0.6086255240660635</v>
       </c>
       <c r="I7" t="n">
-        <v>1.115446784689137</v>
+        <v>0.7967115980511554</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1134603642883</v>
+        <v>-5.268122933548253</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03456138402911084</v>
+        <v>1.378257996723415e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>4.854695197621896</v>
+        <v>22.79065069216779</v>
       </c>
     </row>
     <row r="8">
@@ -774,43 +774,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1330399078232676</v>
+        <v>8.016988523590271</v>
       </c>
       <c r="D8" t="n">
-        <v>1.142295583951561</v>
+        <v>3032.032675518592</v>
       </c>
       <c r="E8" t="n">
-        <v>3.661128535225911</v>
+        <v>0.7103550433532237</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.042640163991401</v>
+        <v>6.624718222381563</v>
       </c>
       <c r="G8" t="n">
-        <v>7.308719979637936</v>
+        <v>9.409258824798979</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008738164952763426</v>
+        <v>753.4918654952718</v>
       </c>
       <c r="I8" t="n">
-        <v>1493.264556310057</v>
+        <v>12200.82467561837</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03633849687144577</v>
+        <v>11.28588949794199</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9710124541336411</v>
+        <v>1.540750470320533e-29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04243829522475152</v>
+        <v>95.71228152023822</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>sigma_</t>
+          <t>rho_</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.500881176157894</v>
+        <v>-0.04108288657619101</v>
       </c>
       <c r="D9" t="n">
-        <v>1.650174724855409</v>
+        <v>0.9597495762944996</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08018860868996533</v>
+        <v>0.08884346142337428</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3437143911551863</v>
+        <v>-0.2152128712278782</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6580479611606016</v>
+        <v>0.1330470980754962</v>
       </c>
       <c r="H9" t="n">
-        <v>1.410175819299746</v>
+        <v>0.8063697689831988</v>
       </c>
       <c r="I9" t="n">
-        <v>1.931019228441902</v>
+        <v>1.142303797374457</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6.246288398573667</v>
+        <v>-0.4624187972642667</v>
       </c>
       <c r="L9" t="n">
-        <v>4.203207796518016e-10</v>
+        <v>0.6437810219953984</v>
       </c>
       <c r="M9" t="n">
-        <v>31.14779016723609</v>
+        <v>0.6353580466158535</v>
       </c>
     </row>
   </sheetData>
